--- a/EXCEL & POWER BI LREANING/04.sample-data-fx-DONE.xlsx
+++ b/EXCEL & POWER BI LREANING/04.sample-data-fx-DONE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Chandoo.org\Courses\FREE DA Course\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aravi\OneDrive\Documents\MY-LEARNINGS\EXCEL &amp; POWER BI LREANING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CCCEF5-C1A5-4562-9500-5A2DB31BFD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7873BF1D-36F2-49A8-B208-95206CC94C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -40,19 +40,22 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2468,13 +2471,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2715,7 +2718,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2727,7 +2730,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2785,7 +2788,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -2800,16 +2803,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2822,7 +2825,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -2839,11 +2842,11 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2858,10 +2861,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="20" formatCode="d\-mmm\-yy"/>
+      <numFmt numFmtId="169" formatCode="d\-mmm\-yy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="10" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3048,62 +3051,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>847725</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>149958</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F92F0C86-81F4-8FF2-79D4-1A937B0920E7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10877550" y="149958"/>
-          <a:ext cx="2486025" cy="707292"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
   <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
@@ -3130,9 +3077,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3170,7 +3117,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3276,7 +3223,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3418,7 +3365,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3427,7 +3374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627306E8-967B-437C-B97A-A3AA7E6942D3}">
   <dimension ref="A1:N265"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
     <col min="2" max="2" width="3.7109375" customWidth="1"/>
@@ -3445,16 +3392,16 @@
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="52.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="C1" s="3" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="5.25" customHeight="1"/>
+    <row r="3" spans="1:14" ht="5.25" customHeight="1"/>
+    <row r="4" spans="1:14" ht="5.25" customHeight="1"/>
+    <row r="5" spans="1:14" ht="21" customHeight="1">
       <c r="C5" s="16"/>
       <c r="D5" s="17" t="s">
         <v>758</v>
@@ -3467,7 +3414,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="21" customHeight="1">
       <c r="C6" s="10">
         <v>1</v>
       </c>
@@ -3485,7 +3432,7 @@
       <c r="J6" s="6"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="21" customHeight="1">
       <c r="C7" s="12">
         <v>2</v>
       </c>
@@ -3501,7 +3448,7 @@
       <c r="J7" s="6"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="21" customHeight="1">
       <c r="C8" s="12">
         <v>3</v>
       </c>
@@ -3519,7 +3466,7 @@
       <c r="J8" s="6"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="21" customHeight="1">
       <c r="C9" s="12">
         <v>4</v>
       </c>
@@ -3535,7 +3482,7 @@
       <c r="J9" s="6"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="21" customHeight="1">
       <c r="C10" s="12">
         <v>5</v>
       </c>
@@ -3553,7 +3500,7 @@
       <c r="J10" s="6"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="21" customHeight="1">
       <c r="C11" s="12">
         <v>6</v>
       </c>
@@ -3569,7 +3516,7 @@
       <c r="J11" s="6"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="21" customHeight="1">
       <c r="C12" s="12">
         <v>7</v>
       </c>
@@ -3587,7 +3534,7 @@
       <c r="J12" s="6"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="21" customHeight="1">
       <c r="C13" s="18">
         <v>8</v>
       </c>
@@ -3603,7 +3550,7 @@
       <c r="J13" s="6"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="21" customHeight="1">
       <c r="C14" s="18">
         <v>9</v>
       </c>
@@ -3621,7 +3568,7 @@
       <c r="J14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="45">
       <c r="C15" s="21">
         <v>10</v>
       </c>
@@ -3639,1252 +3586,1252 @@
       <c r="J15" s="6"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="H16" s="5"/>
       <c r="J16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:14">
       <c r="H17" s="5"/>
       <c r="J17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:14">
       <c r="H18" s="5"/>
       <c r="J18" s="6"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:14">
       <c r="H19" s="5"/>
       <c r="J19" s="6"/>
       <c r="N19" s="4"/>
     </row>
-    <row r="20" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:14">
       <c r="H20" s="5"/>
       <c r="J20" s="6"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:14">
       <c r="H21" s="5"/>
       <c r="J21" s="6"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:14">
       <c r="H22" s="5"/>
       <c r="J22" s="6"/>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="8:14">
       <c r="H23" s="5"/>
       <c r="J23" s="6"/>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="8:14">
       <c r="H24" s="5"/>
       <c r="J24" s="6"/>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:14">
       <c r="H25" s="5"/>
       <c r="J25" s="6"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="8:14">
       <c r="H26" s="5"/>
       <c r="J26" s="6"/>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:14">
       <c r="H27" s="5"/>
       <c r="J27" s="6"/>
       <c r="N27" s="4"/>
     </row>
-    <row r="28" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:14">
       <c r="H28" s="5"/>
       <c r="J28" s="6"/>
       <c r="N28" s="4"/>
     </row>
-    <row r="29" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="8:14">
       <c r="H29" s="5"/>
       <c r="J29" s="6"/>
       <c r="N29" s="4"/>
     </row>
-    <row r="30" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="8:14">
       <c r="H30" s="5"/>
       <c r="J30" s="6"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:14">
       <c r="H31" s="5"/>
       <c r="J31" s="6"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="8:14">
       <c r="H32" s="5"/>
       <c r="J32" s="6"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:14">
       <c r="H33" s="5"/>
       <c r="J33" s="6"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:14">
       <c r="H34" s="5"/>
       <c r="J34" s="6"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:14">
       <c r="H35" s="5"/>
       <c r="J35" s="6"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:14">
       <c r="H36" s="5"/>
       <c r="J36" s="6"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:14">
       <c r="H37" s="5"/>
       <c r="J37" s="6"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:14">
       <c r="H38" s="5"/>
       <c r="J38" s="6"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:14">
       <c r="H39" s="5"/>
       <c r="J39" s="6"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:14">
       <c r="H40" s="5"/>
       <c r="J40" s="6"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:14">
       <c r="H41" s="5"/>
       <c r="J41" s="6"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:14">
       <c r="H42" s="5"/>
       <c r="J42" s="6"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:14">
       <c r="H43" s="5"/>
       <c r="J43" s="6"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:14">
       <c r="H44" s="5"/>
       <c r="J44" s="6"/>
       <c r="N44" s="4"/>
     </row>
-    <row r="45" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:14">
       <c r="H45" s="5"/>
       <c r="J45" s="6"/>
       <c r="N45" s="4"/>
     </row>
-    <row r="46" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:14">
       <c r="H46" s="5"/>
       <c r="J46" s="6"/>
       <c r="N46" s="4"/>
     </row>
-    <row r="47" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:14">
       <c r="H47" s="5"/>
       <c r="J47" s="6"/>
       <c r="N47" s="4"/>
     </row>
-    <row r="48" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:14">
       <c r="H48" s="5"/>
       <c r="J48" s="6"/>
       <c r="N48" s="4"/>
     </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="8:14">
       <c r="H49" s="5"/>
       <c r="J49" s="6"/>
       <c r="N49" s="4"/>
     </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:14">
       <c r="H50" s="5"/>
       <c r="J50" s="6"/>
       <c r="N50" s="4"/>
     </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="8:14">
       <c r="H51" s="5"/>
       <c r="J51" s="6"/>
       <c r="N51" s="4"/>
     </row>
-    <row r="52" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="8:14">
       <c r="H52" s="5"/>
       <c r="J52" s="6"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="8:14">
       <c r="H53" s="5"/>
       <c r="J53" s="6"/>
       <c r="N53" s="4"/>
     </row>
-    <row r="54" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="8:14">
       <c r="H54" s="5"/>
       <c r="J54" s="6"/>
       <c r="N54" s="4"/>
     </row>
-    <row r="55" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="8:14">
       <c r="H55" s="5"/>
       <c r="J55" s="6"/>
       <c r="N55" s="4"/>
     </row>
-    <row r="56" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="8:14">
       <c r="H56" s="5"/>
       <c r="J56" s="6"/>
       <c r="N56" s="4"/>
     </row>
-    <row r="57" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="8:14">
       <c r="H57" s="5"/>
       <c r="J57" s="6"/>
       <c r="N57" s="4"/>
     </row>
-    <row r="58" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="8:14">
       <c r="H58" s="5"/>
       <c r="J58" s="6"/>
       <c r="N58" s="4"/>
     </row>
-    <row r="59" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="8:14">
       <c r="H59" s="5"/>
       <c r="J59" s="6"/>
       <c r="N59" s="4"/>
     </row>
-    <row r="60" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="8:14">
       <c r="H60" s="5"/>
       <c r="J60" s="6"/>
       <c r="N60" s="4"/>
     </row>
-    <row r="61" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="8:14">
       <c r="H61" s="5"/>
       <c r="J61" s="6"/>
       <c r="N61" s="4"/>
     </row>
-    <row r="62" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="8:14">
       <c r="H62" s="5"/>
       <c r="J62" s="6"/>
       <c r="N62" s="4"/>
     </row>
-    <row r="63" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:14">
       <c r="H63" s="5"/>
       <c r="J63" s="6"/>
       <c r="N63" s="4"/>
     </row>
-    <row r="64" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:14">
       <c r="H64" s="5"/>
       <c r="J64" s="6"/>
       <c r="N64" s="4"/>
     </row>
-    <row r="65" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:14">
       <c r="H65" s="5"/>
       <c r="J65" s="6"/>
       <c r="N65" s="4"/>
     </row>
-    <row r="66" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:14">
       <c r="H66" s="5"/>
       <c r="J66" s="6"/>
       <c r="N66" s="4"/>
     </row>
-    <row r="67" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:14">
       <c r="H67" s="5"/>
       <c r="J67" s="6"/>
       <c r="N67" s="4"/>
     </row>
-    <row r="68" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="8:14">
       <c r="H68" s="5"/>
       <c r="J68" s="6"/>
       <c r="N68" s="4"/>
     </row>
-    <row r="69" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="8:14">
       <c r="H69" s="5"/>
       <c r="J69" s="6"/>
       <c r="N69" s="4"/>
     </row>
-    <row r="70" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="8:14">
       <c r="H70" s="5"/>
       <c r="J70" s="6"/>
       <c r="N70" s="4"/>
     </row>
-    <row r="71" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="8:14">
       <c r="H71" s="5"/>
       <c r="J71" s="6"/>
       <c r="N71" s="4"/>
     </row>
-    <row r="72" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="8:14">
       <c r="H72" s="5"/>
       <c r="J72" s="6"/>
       <c r="N72" s="4"/>
     </row>
-    <row r="73" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="8:14">
       <c r="H73" s="5"/>
       <c r="J73" s="6"/>
       <c r="N73" s="4"/>
     </row>
-    <row r="74" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="8:14">
       <c r="H74" s="5"/>
       <c r="J74" s="6"/>
       <c r="N74" s="4"/>
     </row>
-    <row r="75" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="8:14">
       <c r="H75" s="5"/>
       <c r="J75" s="6"/>
       <c r="N75" s="4"/>
     </row>
-    <row r="76" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="8:14">
       <c r="H76" s="5"/>
       <c r="J76" s="6"/>
       <c r="N76" s="4"/>
     </row>
-    <row r="77" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="8:14">
       <c r="H77" s="5"/>
       <c r="J77" s="6"/>
       <c r="N77" s="4"/>
     </row>
-    <row r="78" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="8:14">
       <c r="H78" s="5"/>
       <c r="J78" s="6"/>
       <c r="N78" s="4"/>
     </row>
-    <row r="79" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="8:14">
       <c r="H79" s="5"/>
       <c r="J79" s="6"/>
       <c r="N79" s="4"/>
     </row>
-    <row r="80" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="8:14">
       <c r="H80" s="5"/>
       <c r="J80" s="6"/>
       <c r="N80" s="4"/>
     </row>
-    <row r="81" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:14">
       <c r="H81" s="5"/>
       <c r="J81" s="6"/>
       <c r="N81" s="4"/>
     </row>
-    <row r="82" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:14">
       <c r="H82" s="5"/>
       <c r="J82" s="6"/>
       <c r="N82" s="4"/>
     </row>
-    <row r="83" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:14">
       <c r="H83" s="5"/>
       <c r="J83" s="6"/>
       <c r="N83" s="4"/>
     </row>
-    <row r="84" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:14">
       <c r="H84" s="5"/>
       <c r="J84" s="6"/>
       <c r="N84" s="4"/>
     </row>
-    <row r="85" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:14">
       <c r="H85" s="5"/>
       <c r="J85" s="6"/>
       <c r="N85" s="4"/>
     </row>
-    <row r="86" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="8:14">
       <c r="H86" s="5"/>
       <c r="J86" s="6"/>
       <c r="N86" s="4"/>
     </row>
-    <row r="87" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="8:14">
       <c r="H87" s="5"/>
       <c r="J87" s="6"/>
       <c r="N87" s="4"/>
     </row>
-    <row r="88" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:14">
       <c r="H88" s="5"/>
       <c r="J88" s="6"/>
       <c r="N88" s="4"/>
     </row>
-    <row r="89" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:14">
       <c r="H89" s="5"/>
       <c r="J89" s="6"/>
       <c r="N89" s="4"/>
     </row>
-    <row r="90" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:14">
       <c r="H90" s="5"/>
       <c r="J90" s="6"/>
       <c r="N90" s="4"/>
     </row>
-    <row r="91" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:14">
       <c r="H91" s="5"/>
       <c r="J91" s="6"/>
       <c r="N91" s="4"/>
     </row>
-    <row r="92" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:14">
       <c r="H92" s="5"/>
       <c r="J92" s="6"/>
       <c r="N92" s="4"/>
     </row>
-    <row r="93" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:14">
       <c r="H93" s="5"/>
       <c r="J93" s="6"/>
       <c r="N93" s="4"/>
     </row>
-    <row r="94" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:14">
       <c r="H94" s="5"/>
       <c r="J94" s="6"/>
       <c r="N94" s="4"/>
     </row>
-    <row r="95" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:14">
       <c r="H95" s="5"/>
       <c r="J95" s="6"/>
       <c r="N95" s="4"/>
     </row>
-    <row r="96" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:14">
       <c r="H96" s="5"/>
       <c r="J96" s="6"/>
       <c r="N96" s="4"/>
     </row>
-    <row r="97" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:14">
       <c r="H97" s="5"/>
       <c r="J97" s="6"/>
       <c r="N97" s="4"/>
     </row>
-    <row r="98" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:14">
       <c r="H98" s="5"/>
       <c r="J98" s="6"/>
       <c r="N98" s="4"/>
     </row>
-    <row r="99" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:14">
       <c r="H99" s="5"/>
       <c r="J99" s="6"/>
       <c r="N99" s="4"/>
     </row>
-    <row r="100" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:14">
       <c r="H100" s="5"/>
       <c r="J100" s="6"/>
       <c r="N100" s="4"/>
     </row>
-    <row r="101" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:14">
       <c r="H101" s="5"/>
       <c r="J101" s="6"/>
       <c r="N101" s="4"/>
     </row>
-    <row r="102" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:14">
       <c r="H102" s="5"/>
       <c r="J102" s="6"/>
       <c r="N102" s="4"/>
     </row>
-    <row r="103" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:14">
       <c r="H103" s="5"/>
       <c r="J103" s="6"/>
       <c r="N103" s="4"/>
     </row>
-    <row r="104" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:14">
       <c r="H104" s="5"/>
       <c r="J104" s="6"/>
       <c r="N104" s="4"/>
     </row>
-    <row r="105" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:14">
       <c r="H105" s="5"/>
       <c r="J105" s="6"/>
       <c r="N105" s="4"/>
     </row>
-    <row r="106" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:14">
       <c r="H106" s="5"/>
       <c r="J106" s="6"/>
       <c r="N106" s="4"/>
     </row>
-    <row r="107" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:14">
       <c r="H107" s="5"/>
       <c r="J107" s="6"/>
       <c r="N107" s="4"/>
     </row>
-    <row r="108" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:14">
       <c r="H108" s="5"/>
       <c r="J108" s="6"/>
       <c r="N108" s="4"/>
     </row>
-    <row r="109" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:14">
       <c r="H109" s="5"/>
       <c r="J109" s="6"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:14">
       <c r="H110" s="5"/>
       <c r="J110" s="6"/>
       <c r="N110" s="4"/>
     </row>
-    <row r="111" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:14">
       <c r="H111" s="5"/>
       <c r="J111" s="6"/>
       <c r="N111" s="4"/>
     </row>
-    <row r="112" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:14">
       <c r="H112" s="5"/>
       <c r="J112" s="6"/>
       <c r="N112" s="4"/>
     </row>
-    <row r="113" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="8:14">
       <c r="H113" s="5"/>
       <c r="J113" s="6"/>
       <c r="N113" s="4"/>
     </row>
-    <row r="114" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="8:14">
       <c r="H114" s="5"/>
       <c r="J114" s="6"/>
       <c r="N114" s="4"/>
     </row>
-    <row r="115" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:14">
       <c r="H115" s="5"/>
       <c r="J115" s="6"/>
       <c r="N115" s="4"/>
     </row>
-    <row r="116" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="8:14">
       <c r="H116" s="5"/>
       <c r="J116" s="6"/>
       <c r="N116" s="4"/>
     </row>
-    <row r="117" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="8:14">
       <c r="H117" s="5"/>
       <c r="J117" s="6"/>
       <c r="N117" s="4"/>
     </row>
-    <row r="118" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="8:14">
       <c r="H118" s="5"/>
       <c r="J118" s="6"/>
       <c r="N118" s="4"/>
     </row>
-    <row r="119" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="8:14">
       <c r="H119" s="5"/>
       <c r="J119" s="6"/>
       <c r="N119" s="4"/>
     </row>
-    <row r="120" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="8:14">
       <c r="H120" s="5"/>
       <c r="J120" s="6"/>
       <c r="N120" s="4"/>
     </row>
-    <row r="121" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:14">
       <c r="H121" s="5"/>
       <c r="J121" s="6"/>
       <c r="N121" s="4"/>
     </row>
-    <row r="122" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="8:14">
       <c r="H122" s="5"/>
       <c r="J122" s="6"/>
       <c r="N122" s="4"/>
     </row>
-    <row r="123" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:14">
       <c r="H123" s="5"/>
       <c r="J123" s="6"/>
       <c r="N123" s="4"/>
     </row>
-    <row r="124" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="8:14">
       <c r="H124" s="5"/>
       <c r="J124" s="6"/>
       <c r="N124" s="4"/>
     </row>
-    <row r="125" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="8:14">
       <c r="H125" s="5"/>
       <c r="J125" s="6"/>
       <c r="N125" s="4"/>
     </row>
-    <row r="126" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:14">
       <c r="H126" s="5"/>
       <c r="J126" s="6"/>
       <c r="N126" s="4"/>
     </row>
-    <row r="127" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:14">
       <c r="H127" s="5"/>
       <c r="J127" s="6"/>
       <c r="N127" s="4"/>
     </row>
-    <row r="128" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:14">
       <c r="H128" s="5"/>
       <c r="J128" s="6"/>
       <c r="N128" s="4"/>
     </row>
-    <row r="129" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="8:14">
       <c r="H129" s="5"/>
       <c r="J129" s="6"/>
       <c r="N129" s="4"/>
     </row>
-    <row r="130" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:14">
       <c r="H130" s="5"/>
       <c r="J130" s="6"/>
       <c r="N130" s="4"/>
     </row>
-    <row r="131" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:14">
       <c r="H131" s="5"/>
       <c r="J131" s="6"/>
       <c r="N131" s="4"/>
     </row>
-    <row r="132" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:14">
       <c r="H132" s="5"/>
       <c r="J132" s="6"/>
       <c r="N132" s="4"/>
     </row>
-    <row r="133" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:14">
       <c r="H133" s="5"/>
       <c r="J133" s="6"/>
       <c r="N133" s="4"/>
     </row>
-    <row r="134" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:14">
       <c r="H134" s="5"/>
       <c r="J134" s="6"/>
       <c r="N134" s="4"/>
     </row>
-    <row r="135" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:14">
       <c r="H135" s="5"/>
       <c r="J135" s="6"/>
       <c r="N135" s="4"/>
     </row>
-    <row r="136" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:14">
       <c r="H136" s="5"/>
       <c r="J136" s="6"/>
       <c r="N136" s="4"/>
     </row>
-    <row r="137" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:14">
       <c r="H137" s="5"/>
       <c r="J137" s="6"/>
       <c r="N137" s="4"/>
     </row>
-    <row r="138" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:14">
       <c r="H138" s="5"/>
       <c r="J138" s="6"/>
       <c r="N138" s="4"/>
     </row>
-    <row r="139" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:14">
       <c r="H139" s="5"/>
       <c r="J139" s="6"/>
       <c r="N139" s="4"/>
     </row>
-    <row r="140" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:14">
       <c r="H140" s="5"/>
       <c r="J140" s="6"/>
       <c r="N140" s="4"/>
     </row>
-    <row r="141" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="8:14">
       <c r="H141" s="5"/>
       <c r="J141" s="6"/>
       <c r="N141" s="4"/>
     </row>
-    <row r="142" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="8:14">
       <c r="H142" s="5"/>
       <c r="J142" s="6"/>
       <c r="N142" s="4"/>
     </row>
-    <row r="143" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="8:14">
       <c r="H143" s="5"/>
       <c r="J143" s="6"/>
       <c r="N143" s="4"/>
     </row>
-    <row r="144" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="8:14">
       <c r="H144" s="5"/>
       <c r="J144" s="6"/>
       <c r="N144" s="4"/>
     </row>
-    <row r="145" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="8:14">
       <c r="H145" s="5"/>
       <c r="J145" s="6"/>
       <c r="N145" s="4"/>
     </row>
-    <row r="146" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="8:14">
       <c r="H146" s="5"/>
       <c r="J146" s="6"/>
       <c r="N146" s="4"/>
     </row>
-    <row r="147" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="8:14">
       <c r="H147" s="5"/>
       <c r="J147" s="6"/>
       <c r="N147" s="4"/>
     </row>
-    <row r="148" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:14">
       <c r="H148" s="5"/>
       <c r="J148" s="6"/>
       <c r="N148" s="4"/>
     </row>
-    <row r="149" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="8:14">
       <c r="H149" s="5"/>
       <c r="J149" s="6"/>
       <c r="N149" s="4"/>
     </row>
-    <row r="150" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:14">
       <c r="H150" s="5"/>
       <c r="J150" s="6"/>
       <c r="N150" s="4"/>
     </row>
-    <row r="151" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:14">
       <c r="H151" s="5"/>
       <c r="J151" s="6"/>
       <c r="N151" s="4"/>
     </row>
-    <row r="152" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:14">
       <c r="H152" s="5"/>
       <c r="J152" s="6"/>
       <c r="N152" s="4"/>
     </row>
-    <row r="153" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:14">
       <c r="H153" s="5"/>
       <c r="J153" s="6"/>
       <c r="N153" s="4"/>
     </row>
-    <row r="154" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:14">
       <c r="H154" s="5"/>
       <c r="J154" s="6"/>
       <c r="N154" s="4"/>
     </row>
-    <row r="155" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:14">
       <c r="H155" s="5"/>
       <c r="J155" s="6"/>
       <c r="N155" s="4"/>
     </row>
-    <row r="156" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:14">
       <c r="H156" s="5"/>
       <c r="J156" s="6"/>
       <c r="N156" s="4"/>
     </row>
-    <row r="157" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:14">
       <c r="H157" s="5"/>
       <c r="J157" s="6"/>
       <c r="N157" s="4"/>
     </row>
-    <row r="158" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="8:14">
       <c r="H158" s="5"/>
       <c r="J158" s="6"/>
       <c r="N158" s="4"/>
     </row>
-    <row r="159" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:14">
       <c r="H159" s="5"/>
       <c r="J159" s="6"/>
       <c r="N159" s="4"/>
     </row>
-    <row r="160" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:14">
       <c r="H160" s="5"/>
       <c r="J160" s="6"/>
       <c r="N160" s="4"/>
     </row>
-    <row r="161" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:14">
       <c r="H161" s="5"/>
       <c r="J161" s="6"/>
       <c r="N161" s="4"/>
     </row>
-    <row r="162" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:14">
       <c r="H162" s="5"/>
       <c r="J162" s="6"/>
       <c r="N162" s="4"/>
     </row>
-    <row r="163" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:14">
       <c r="H163" s="5"/>
       <c r="J163" s="6"/>
       <c r="N163" s="4"/>
     </row>
-    <row r="164" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:14">
       <c r="H164" s="5"/>
       <c r="J164" s="6"/>
       <c r="N164" s="4"/>
     </row>
-    <row r="165" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="8:14">
       <c r="H165" s="5"/>
       <c r="J165" s="6"/>
       <c r="N165" s="4"/>
     </row>
-    <row r="166" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="8:14">
       <c r="H166" s="5"/>
       <c r="J166" s="6"/>
       <c r="N166" s="4"/>
     </row>
-    <row r="167" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="8:14">
       <c r="H167" s="5"/>
       <c r="J167" s="6"/>
       <c r="N167" s="4"/>
     </row>
-    <row r="168" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="8:14">
       <c r="H168" s="5"/>
       <c r="J168" s="6"/>
       <c r="N168" s="4"/>
     </row>
-    <row r="169" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="8:14">
       <c r="H169" s="5"/>
       <c r="J169" s="6"/>
       <c r="N169" s="4"/>
     </row>
-    <row r="170" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="8:14">
       <c r="H170" s="5"/>
       <c r="J170" s="6"/>
       <c r="N170" s="4"/>
     </row>
-    <row r="171" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="8:14">
       <c r="H171" s="5"/>
       <c r="J171" s="6"/>
       <c r="N171" s="4"/>
     </row>
-    <row r="172" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="8:14">
       <c r="H172" s="5"/>
       <c r="J172" s="6"/>
       <c r="N172" s="4"/>
     </row>
-    <row r="173" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="8:14">
       <c r="H173" s="5"/>
       <c r="J173" s="6"/>
       <c r="N173" s="4"/>
     </row>
-    <row r="174" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:14">
       <c r="H174" s="5"/>
       <c r="J174" s="6"/>
       <c r="N174" s="4"/>
     </row>
-    <row r="175" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="8:14">
       <c r="H175" s="5"/>
       <c r="J175" s="6"/>
       <c r="N175" s="4"/>
     </row>
-    <row r="176" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="8:14">
       <c r="H176" s="5"/>
       <c r="J176" s="6"/>
       <c r="N176" s="4"/>
     </row>
-    <row r="177" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="8:14">
       <c r="H177" s="5"/>
       <c r="J177" s="6"/>
       <c r="N177" s="4"/>
     </row>
-    <row r="178" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="8:14">
       <c r="H178" s="5"/>
       <c r="J178" s="6"/>
       <c r="N178" s="4"/>
     </row>
-    <row r="179" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:14">
       <c r="H179" s="5"/>
       <c r="J179" s="6"/>
       <c r="N179" s="4"/>
     </row>
-    <row r="180" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="8:14">
       <c r="H180" s="5"/>
       <c r="J180" s="6"/>
       <c r="N180" s="4"/>
     </row>
-    <row r="181" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="8:14">
       <c r="H181" s="5"/>
       <c r="J181" s="6"/>
       <c r="N181" s="4"/>
     </row>
-    <row r="182" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="8:14">
       <c r="H182" s="5"/>
       <c r="J182" s="6"/>
       <c r="N182" s="4"/>
     </row>
-    <row r="183" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="8:14">
       <c r="H183" s="5"/>
       <c r="J183" s="6"/>
       <c r="N183" s="4"/>
     </row>
-    <row r="184" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="8:14">
       <c r="H184" s="5"/>
       <c r="J184" s="6"/>
       <c r="N184" s="4"/>
     </row>
-    <row r="185" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="8:14">
       <c r="H185" s="5"/>
       <c r="J185" s="6"/>
       <c r="N185" s="4"/>
     </row>
-    <row r="186" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="8:14">
       <c r="H186" s="5"/>
       <c r="J186" s="6"/>
       <c r="N186" s="4"/>
     </row>
-    <row r="187" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="8:14">
       <c r="H187" s="5"/>
       <c r="J187" s="6"/>
       <c r="N187" s="4"/>
     </row>
-    <row r="188" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="8:14">
       <c r="H188" s="5"/>
       <c r="J188" s="6"/>
       <c r="N188" s="4"/>
     </row>
-    <row r="189" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:14">
       <c r="H189" s="5"/>
       <c r="J189" s="6"/>
       <c r="N189" s="4"/>
     </row>
-    <row r="190" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="8:14">
       <c r="H190" s="5"/>
       <c r="J190" s="6"/>
       <c r="N190" s="4"/>
     </row>
-    <row r="191" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="8:14">
       <c r="H191" s="5"/>
       <c r="J191" s="6"/>
       <c r="N191" s="4"/>
     </row>
-    <row r="192" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="8:14">
       <c r="H192" s="5"/>
       <c r="J192" s="6"/>
       <c r="N192" s="4"/>
     </row>
-    <row r="193" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="8:14">
       <c r="H193" s="5"/>
       <c r="J193" s="6"/>
       <c r="N193" s="4"/>
     </row>
-    <row r="194" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="8:14">
       <c r="H194" s="5"/>
       <c r="J194" s="6"/>
       <c r="N194" s="4"/>
     </row>
-    <row r="195" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="8:14">
       <c r="H195" s="5"/>
       <c r="J195" s="6"/>
       <c r="N195" s="4"/>
     </row>
-    <row r="196" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="8:14">
       <c r="H196" s="5"/>
       <c r="J196" s="6"/>
       <c r="N196" s="4"/>
     </row>
-    <row r="197" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="8:14">
       <c r="H197" s="5"/>
       <c r="J197" s="6"/>
       <c r="N197" s="4"/>
     </row>
-    <row r="198" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="8:14">
       <c r="H198" s="5"/>
       <c r="J198" s="6"/>
       <c r="N198" s="4"/>
     </row>
-    <row r="199" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="8:14">
       <c r="H199" s="5"/>
       <c r="J199" s="6"/>
       <c r="N199" s="4"/>
     </row>
-    <row r="200" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="8:14">
       <c r="H200" s="5"/>
       <c r="J200" s="6"/>
       <c r="N200" s="4"/>
     </row>
-    <row r="201" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="8:14">
       <c r="H201" s="5"/>
       <c r="J201" s="6"/>
       <c r="N201" s="4"/>
     </row>
-    <row r="202" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="8:14">
       <c r="H202" s="5"/>
       <c r="J202" s="6"/>
       <c r="N202" s="4"/>
     </row>
-    <row r="203" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="8:14">
       <c r="H203" s="5"/>
       <c r="J203" s="6"/>
       <c r="N203" s="4"/>
     </row>
-    <row r="204" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="8:14">
       <c r="H204" s="5"/>
       <c r="J204" s="6"/>
       <c r="N204" s="4"/>
     </row>
-    <row r="205" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="8:14">
       <c r="H205" s="5"/>
       <c r="J205" s="6"/>
       <c r="N205" s="4"/>
     </row>
-    <row r="206" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="8:14">
       <c r="H206" s="5"/>
       <c r="J206" s="6"/>
       <c r="N206" s="4"/>
     </row>
-    <row r="207" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:14">
       <c r="H207" s="5"/>
       <c r="J207" s="6"/>
       <c r="N207" s="4"/>
     </row>
-    <row r="208" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="8:14">
       <c r="H208" s="5"/>
       <c r="J208" s="6"/>
       <c r="N208" s="4"/>
     </row>
-    <row r="209" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="8:14">
       <c r="H209" s="5"/>
       <c r="J209" s="6"/>
       <c r="N209" s="4"/>
     </row>
-    <row r="210" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="8:14">
       <c r="H210" s="5"/>
       <c r="J210" s="6"/>
       <c r="N210" s="4"/>
     </row>
-    <row r="211" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="8:14">
       <c r="H211" s="5"/>
       <c r="J211" s="6"/>
       <c r="N211" s="4"/>
     </row>
-    <row r="212" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="8:14">
       <c r="H212" s="5"/>
       <c r="J212" s="6"/>
       <c r="N212" s="4"/>
     </row>
-    <row r="213" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="8:14">
       <c r="H213" s="5"/>
       <c r="J213" s="6"/>
       <c r="N213" s="4"/>
     </row>
-    <row r="214" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="8:14">
       <c r="H214" s="5"/>
       <c r="J214" s="6"/>
       <c r="N214" s="4"/>
     </row>
-    <row r="215" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="8:14">
       <c r="H215" s="5"/>
       <c r="J215" s="6"/>
       <c r="N215" s="4"/>
     </row>
-    <row r="216" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="8:14">
       <c r="H216" s="5"/>
       <c r="J216" s="6"/>
       <c r="N216" s="4"/>
     </row>
-    <row r="217" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="8:14">
       <c r="H217" s="5"/>
       <c r="J217" s="6"/>
       <c r="N217" s="4"/>
     </row>
-    <row r="218" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="8:14">
       <c r="H218" s="5"/>
       <c r="J218" s="6"/>
       <c r="N218" s="4"/>
     </row>
-    <row r="219" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="8:14">
       <c r="H219" s="5"/>
       <c r="J219" s="6"/>
       <c r="N219" s="4"/>
     </row>
-    <row r="220" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="8:14">
       <c r="H220" s="5"/>
       <c r="J220" s="6"/>
       <c r="N220" s="4"/>
     </row>
-    <row r="221" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="8:14">
       <c r="H221" s="5"/>
       <c r="J221" s="6"/>
       <c r="N221" s="4"/>
     </row>
-    <row r="222" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="8:14">
       <c r="H222" s="5"/>
       <c r="J222" s="6"/>
       <c r="N222" s="4"/>
     </row>
-    <row r="223" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="8:14">
       <c r="H223" s="5"/>
       <c r="J223" s="6"/>
       <c r="N223" s="4"/>
     </row>
-    <row r="224" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="8:14">
       <c r="H224" s="5"/>
       <c r="J224" s="6"/>
       <c r="N224" s="4"/>
     </row>
-    <row r="225" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="8:14">
       <c r="H225" s="5"/>
       <c r="J225" s="6"/>
       <c r="N225" s="4"/>
     </row>
-    <row r="226" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="8:14">
       <c r="H226" s="5"/>
       <c r="J226" s="6"/>
       <c r="N226" s="4"/>
     </row>
-    <row r="227" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="8:14">
       <c r="H227" s="5"/>
       <c r="J227" s="6"/>
       <c r="N227" s="4"/>
     </row>
-    <row r="228" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="8:14">
       <c r="H228" s="5"/>
       <c r="J228" s="6"/>
       <c r="N228" s="4"/>
     </row>
-    <row r="229" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="8:14">
       <c r="H229" s="5"/>
       <c r="J229" s="6"/>
       <c r="N229" s="4"/>
     </row>
-    <row r="230" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="8:14">
       <c r="H230" s="5"/>
       <c r="J230" s="6"/>
       <c r="N230" s="4"/>
     </row>
-    <row r="231" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="8:14">
       <c r="H231" s="5"/>
       <c r="J231" s="6"/>
       <c r="N231" s="4"/>
     </row>
-    <row r="232" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="8:14">
       <c r="H232" s="5"/>
       <c r="J232" s="6"/>
       <c r="N232" s="4"/>
     </row>
-    <row r="233" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="8:14">
       <c r="H233" s="5"/>
       <c r="J233" s="6"/>
       <c r="N233" s="4"/>
     </row>
-    <row r="234" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="8:14">
       <c r="H234" s="5"/>
       <c r="J234" s="6"/>
       <c r="N234" s="4"/>
     </row>
-    <row r="235" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="8:14">
       <c r="H235" s="5"/>
       <c r="J235" s="6"/>
       <c r="N235" s="4"/>
     </row>
-    <row r="236" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="8:14">
       <c r="H236" s="5"/>
       <c r="J236" s="6"/>
       <c r="N236" s="4"/>
     </row>
-    <row r="237" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="8:14">
       <c r="H237" s="5"/>
       <c r="J237" s="6"/>
       <c r="N237" s="4"/>
     </row>
-    <row r="238" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="8:14">
       <c r="H238" s="5"/>
       <c r="J238" s="6"/>
       <c r="N238" s="4"/>
     </row>
-    <row r="239" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:14">
       <c r="H239" s="5"/>
       <c r="J239" s="6"/>
       <c r="N239" s="4"/>
     </row>
-    <row r="240" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="8:14">
       <c r="H240" s="5"/>
       <c r="J240" s="6"/>
       <c r="N240" s="4"/>
     </row>
-    <row r="241" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="8:14">
       <c r="H241" s="5"/>
       <c r="J241" s="6"/>
       <c r="N241" s="4"/>
     </row>
-    <row r="242" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="8:14">
       <c r="H242" s="5"/>
       <c r="J242" s="6"/>
       <c r="N242" s="4"/>
     </row>
-    <row r="243" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="8:14">
       <c r="H243" s="5"/>
       <c r="J243" s="6"/>
       <c r="N243" s="4"/>
     </row>
-    <row r="244" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="8:14">
       <c r="H244" s="5"/>
       <c r="J244" s="6"/>
       <c r="N244" s="4"/>
     </row>
-    <row r="245" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="8:14">
       <c r="H245" s="5"/>
       <c r="J245" s="6"/>
       <c r="N245" s="4"/>
     </row>
-    <row r="246" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="8:14">
       <c r="H246" s="5"/>
       <c r="J246" s="6"/>
       <c r="N246" s="4"/>
     </row>
-    <row r="247" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:14">
       <c r="H247" s="5"/>
       <c r="J247" s="6"/>
       <c r="N247" s="4"/>
     </row>
-    <row r="248" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="8:14">
       <c r="H248" s="5"/>
       <c r="J248" s="6"/>
       <c r="N248" s="4"/>
     </row>
-    <row r="249" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="8:14">
       <c r="H249" s="5"/>
       <c r="J249" s="6"/>
       <c r="N249" s="4"/>
     </row>
-    <row r="250" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="8:14">
       <c r="H250" s="5"/>
       <c r="J250" s="6"/>
       <c r="N250" s="4"/>
     </row>
-    <row r="251" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="8:14">
       <c r="H251" s="5"/>
       <c r="J251" s="6"/>
       <c r="N251" s="4"/>
     </row>
-    <row r="252" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="8:14">
       <c r="H252" s="5"/>
       <c r="J252" s="6"/>
       <c r="N252" s="4"/>
     </row>
-    <row r="253" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="8:14">
       <c r="H253" s="5"/>
       <c r="J253" s="6"/>
       <c r="N253" s="4"/>
     </row>
-    <row r="254" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="8:14">
       <c r="H254" s="5"/>
       <c r="J254" s="6"/>
       <c r="N254" s="4"/>
     </row>
-    <row r="255" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="8:14">
       <c r="H255" s="5"/>
       <c r="J255" s="6"/>
       <c r="N255" s="4"/>
     </row>
-    <row r="256" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="8:14">
       <c r="H256" s="5"/>
       <c r="J256" s="6"/>
       <c r="N256" s="4"/>
     </row>
-    <row r="257" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="8:14">
       <c r="H257" s="5"/>
       <c r="J257" s="6"/>
       <c r="N257" s="4"/>
     </row>
-    <row r="258" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="8:14">
       <c r="H258" s="5"/>
       <c r="J258" s="6"/>
       <c r="N258" s="4"/>
     </row>
-    <row r="259" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="8:14">
       <c r="H259" s="5"/>
       <c r="J259" s="6"/>
       <c r="N259" s="4"/>
     </row>
-    <row r="260" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="8:14">
       <c r="H260" s="5"/>
       <c r="J260" s="6"/>
       <c r="N260" s="4"/>
     </row>
-    <row r="261" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="8:14">
       <c r="H261" s="5"/>
       <c r="J261" s="6"/>
       <c r="N261" s="4"/>
     </row>
-    <row r="262" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="8:14">
       <c r="H262" s="5"/>
       <c r="J262" s="6"/>
       <c r="N262" s="4"/>
     </row>
-    <row r="263" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="8:14">
       <c r="H263" s="5"/>
       <c r="J263" s="6"/>
       <c r="N263" s="4"/>
     </row>
-    <row r="264" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="8:14">
       <c r="H264" s="5"/>
       <c r="J264" s="6"/>
       <c r="N264" s="4"/>
     </row>
-    <row r="265" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="8:14">
       <c r="H265" s="5"/>
       <c r="J265" s="6"/>
       <c r="N265" s="4"/>
@@ -4898,7 +4845,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
     <col min="2" max="2" width="3.7109375" customWidth="1"/>
@@ -4916,13 +4863,13 @@
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="52.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="C1" s="3" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="C7" t="s">
         <v>0</v>
       </c>
@@ -4963,7 +4910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="C8" t="s">
         <v>627</v>
       </c>
@@ -5004,7 +4951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="C9" t="s">
         <v>309</v>
       </c>
@@ -5045,7 +4992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="C10" t="s">
         <v>608</v>
       </c>
@@ -5086,7 +5033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="C11" t="s">
         <v>608</v>
       </c>
@@ -5127,7 +5074,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="C12" t="s">
         <v>12</v>
       </c>
@@ -5168,7 +5115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="C13" t="s">
         <v>645</v>
       </c>
@@ -5209,7 +5156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="C14" t="s">
         <v>59</v>
       </c>
@@ -5250,7 +5197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="C15" t="s">
         <v>225</v>
       </c>
@@ -5291,7 +5238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="C16" t="s">
         <v>504</v>
       </c>
@@ -5332,7 +5279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:15">
       <c r="C17" t="s">
         <v>596</v>
       </c>
@@ -5373,7 +5320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:15">
       <c r="C18" t="s">
         <v>98</v>
       </c>
@@ -5414,7 +5361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:15">
       <c r="C19" t="s">
         <v>94</v>
       </c>
@@ -5455,7 +5402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:15">
       <c r="C20" t="s">
         <v>291</v>
       </c>
@@ -5496,7 +5443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:15">
       <c r="C21" t="s">
         <v>590</v>
       </c>
@@ -5537,7 +5484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:15">
       <c r="C22" t="s">
         <v>276</v>
       </c>
@@ -5578,7 +5525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:15">
       <c r="C23" t="s">
         <v>294</v>
       </c>
@@ -5619,7 +5566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:15">
       <c r="C24" t="s">
         <v>548</v>
       </c>
@@ -5660,7 +5607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:15">
       <c r="C25" t="s">
         <v>698</v>
       </c>
@@ -5701,7 +5648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:15">
       <c r="C26" t="s">
         <v>246</v>
       </c>
@@ -5742,7 +5689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:15">
       <c r="C27" t="s">
         <v>609</v>
       </c>
@@ -5783,7 +5730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:15">
       <c r="C28" t="s">
         <v>666</v>
       </c>
@@ -5824,7 +5771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:15">
       <c r="C29" t="s">
         <v>141</v>
       </c>
@@ -5865,7 +5812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:15">
       <c r="C30" t="s">
         <v>672</v>
       </c>
@@ -5906,7 +5853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:15">
       <c r="C31" t="s">
         <v>389</v>
       </c>
@@ -5947,7 +5894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:15">
       <c r="C32" t="s">
         <v>389</v>
       </c>
@@ -5988,7 +5935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:15">
       <c r="C33" t="s">
         <v>336</v>
       </c>
@@ -6029,7 +5976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:15">
       <c r="C34" t="s">
         <v>533</v>
       </c>
@@ -6070,7 +6017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:15">
       <c r="C35" t="s">
         <v>342</v>
       </c>
@@ -6111,7 +6058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:15">
       <c r="C36" t="s">
         <v>392</v>
       </c>
@@ -6152,7 +6099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:15">
       <c r="C37" t="s">
         <v>189</v>
       </c>
@@ -6193,7 +6140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:15">
       <c r="C38" t="s">
         <v>575</v>
       </c>
@@ -6234,7 +6181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:15">
       <c r="C39" t="s">
         <v>121</v>
       </c>
@@ -6275,7 +6222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:15">
       <c r="C40" t="s">
         <v>445</v>
       </c>
@@ -6316,7 +6263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:15">
       <c r="C41" t="s">
         <v>707</v>
       </c>
@@ -6357,7 +6304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:15">
       <c r="C42" t="s">
         <v>115</v>
       </c>
@@ -6398,7 +6345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:15">
       <c r="C43" t="s">
         <v>216</v>
       </c>
@@ -6439,7 +6386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:15">
       <c r="C44" t="s">
         <v>560</v>
       </c>
@@ -6480,7 +6427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:15">
       <c r="C45" t="s">
         <v>273</v>
       </c>
@@ -6521,7 +6468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:15">
       <c r="C46" t="s">
         <v>642</v>
       </c>
@@ -6562,7 +6509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:15">
       <c r="C47" t="s">
         <v>118</v>
       </c>
@@ -6603,7 +6550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:15">
       <c r="C48" t="s">
         <v>469</v>
       </c>
@@ -6644,7 +6591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:15">
       <c r="C49" t="s">
         <v>102</v>
       </c>
@@ -6685,7 +6632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:15">
       <c r="C50" t="s">
         <v>721</v>
       </c>
@@ -6726,7 +6673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:15">
       <c r="C51" t="s">
         <v>321</v>
       </c>
@@ -6767,7 +6714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:15">
       <c r="C52" t="s">
         <v>321</v>
       </c>
@@ -6808,7 +6755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:15">
       <c r="C53" t="s">
         <v>198</v>
       </c>
@@ -6849,7 +6796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:15">
       <c r="C54" t="s">
         <v>501</v>
       </c>
@@ -6890,7 +6837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:15">
       <c r="C55" t="s">
         <v>258</v>
       </c>
@@ -6931,7 +6878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:15">
       <c r="C56" t="s">
         <v>728</v>
       </c>
@@ -6972,7 +6919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:15">
       <c r="C57" t="s">
         <v>282</v>
       </c>
@@ -7013,7 +6960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:15">
       <c r="C58" t="s">
         <v>413</v>
       </c>
@@ -7054,7 +7001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:15">
       <c r="C59" t="s">
         <v>69</v>
       </c>
@@ -7095,7 +7042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:15">
       <c r="C60" t="s">
         <v>46</v>
       </c>
@@ -7136,7 +7083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:15">
       <c r="C61" t="s">
         <v>21</v>
       </c>
@@ -7177,7 +7124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:15">
       <c r="C62" t="s">
         <v>624</v>
       </c>
@@ -7218,7 +7165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:15">
       <c r="C63" t="s">
         <v>434</v>
       </c>
@@ -7259,7 +7206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:15">
       <c r="C64" t="s">
         <v>578</v>
       </c>
@@ -7300,7 +7247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>510</v>
       </c>
@@ -7341,7 +7288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>42</v>
       </c>
@@ -7382,7 +7329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>605</v>
       </c>
@@ -7423,7 +7370,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>657</v>
       </c>
@@ -7464,7 +7411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>186</v>
       </c>
@@ -7505,7 +7452,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>318</v>
       </c>
@@ -7546,7 +7493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>339</v>
       </c>
@@ -7587,7 +7534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>55</v>
       </c>
@@ -7628,7 +7575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>78</v>
       </c>
@@ -7669,7 +7616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>365</v>
       </c>
@@ -7710,7 +7657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>210</v>
       </c>
@@ -7751,7 +7698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>210</v>
       </c>
@@ -7792,7 +7739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>407</v>
       </c>
@@ -7833,7 +7780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>419</v>
       </c>
@@ -7874,7 +7821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>162</v>
       </c>
@@ -7915,7 +7862,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>416</v>
       </c>
@@ -7956,7 +7903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:15">
       <c r="C81" t="s">
         <v>128</v>
       </c>
@@ -7997,7 +7944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:15">
       <c r="C82" t="s">
         <v>183</v>
       </c>
@@ -8038,7 +7985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:15">
       <c r="C83" t="s">
         <v>351</v>
       </c>
@@ -8079,7 +8026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:15">
       <c r="C84" t="s">
         <v>147</v>
       </c>
@@ -8120,7 +8067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:15">
       <c r="C85" t="s">
         <v>192</v>
       </c>
@@ -8161,7 +8108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:15">
       <c r="C86" t="s">
         <v>348</v>
       </c>
@@ -8202,7 +8149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:15">
       <c r="C87" t="s">
         <v>566</v>
       </c>
@@ -8243,7 +8190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:15">
       <c r="C88" t="s">
         <v>431</v>
       </c>
@@ -8284,7 +8231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:15">
       <c r="C89" t="s">
         <v>51</v>
       </c>
@@ -8325,7 +8272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:15">
       <c r="C90" t="s">
         <v>410</v>
       </c>
@@ -8366,7 +8313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:15">
       <c r="C91" t="s">
         <v>410</v>
       </c>
@@ -8407,7 +8354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:15">
       <c r="C92" t="s">
         <v>654</v>
       </c>
@@ -8448,7 +8395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:15">
       <c r="C93" t="s">
         <v>654</v>
       </c>
@@ -8489,7 +8436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:15">
       <c r="C94" t="s">
         <v>557</v>
       </c>
@@ -8530,7 +8477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:15">
       <c r="C95" t="s">
         <v>333</v>
       </c>
@@ -8571,7 +8518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:15">
       <c r="C96" t="s">
         <v>204</v>
       </c>
@@ -8612,7 +8559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:15">
       <c r="C97" t="s">
         <v>648</v>
       </c>
@@ -8653,7 +8600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:15">
       <c r="C98" t="s">
         <v>513</v>
       </c>
@@ -8694,7 +8641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:15">
       <c r="C99" t="s">
         <v>633</v>
       </c>
@@ -8735,7 +8682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:15">
       <c r="C100" t="s">
         <v>213</v>
       </c>
@@ -8776,7 +8723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:15">
       <c r="C101" t="s">
         <v>132</v>
       </c>
@@ -8817,7 +8764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:15">
       <c r="C102" t="s">
         <v>132</v>
       </c>
@@ -8858,7 +8805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:15">
       <c r="C103" t="s">
         <v>685</v>
       </c>
@@ -8899,7 +8846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:15">
       <c r="C104" t="s">
         <v>688</v>
       </c>
@@ -8940,7 +8887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:15">
       <c r="C105" t="s">
         <v>682</v>
       </c>
@@ -8981,7 +8928,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:15">
       <c r="C106" t="s">
         <v>451</v>
       </c>
@@ -9022,7 +8969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:15">
       <c r="C107" t="s">
         <v>487</v>
       </c>
@@ -9063,7 +9010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:15">
       <c r="C108" t="s">
         <v>519</v>
       </c>
@@ -9104,7 +9051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:15">
       <c r="C109" t="s">
         <v>234</v>
       </c>
@@ -9145,7 +9092,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:15">
       <c r="C110" t="s">
         <v>234</v>
       </c>
@@ -9186,7 +9133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:15">
       <c r="C111" t="s">
         <v>669</v>
       </c>
@@ -9227,7 +9174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:15">
       <c r="C112" t="s">
         <v>448</v>
       </c>
@@ -9268,7 +9215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:15">
       <c r="C113" t="s">
         <v>360</v>
       </c>
@@ -9309,7 +9256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:15">
       <c r="C114" t="s">
         <v>240</v>
       </c>
@@ -9350,7 +9297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:15">
       <c r="C115" t="s">
         <v>240</v>
       </c>
@@ -9391,7 +9338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:15">
       <c r="C116" t="s">
         <v>507</v>
       </c>
@@ -9432,7 +9379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:15">
       <c r="C117" t="s">
         <v>279</v>
       </c>
@@ -9473,7 +9420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:15">
       <c r="C118" t="s">
         <v>630</v>
       </c>
@@ -9514,7 +9461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:15">
       <c r="C119" t="s">
         <v>312</v>
       </c>
@@ -9555,7 +9502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:15">
       <c r="C120" t="s">
         <v>735</v>
       </c>
@@ -9596,7 +9543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:15">
       <c r="C121" t="s">
         <v>395</v>
       </c>
@@ -9637,7 +9584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:15">
       <c r="C122" t="s">
         <v>525</v>
       </c>
@@ -9678,7 +9625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:15">
       <c r="C123" t="s">
         <v>593</v>
       </c>
@@ -9719,7 +9666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:15">
       <c r="C124" t="s">
         <v>324</v>
       </c>
@@ -9760,7 +9707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:15">
       <c r="C125" t="s">
         <v>88</v>
       </c>
@@ -9801,7 +9748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:15">
       <c r="C126" t="s">
         <v>368</v>
       </c>
@@ -9842,7 +9789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:15">
       <c r="C127" t="s">
         <v>29</v>
       </c>
@@ -9883,7 +9830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:15">
       <c r="C128" t="s">
         <v>704</v>
       </c>
@@ -9924,7 +9871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:15">
       <c r="C129" t="s">
         <v>460</v>
       </c>
@@ -9965,7 +9912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:15">
       <c r="C130" t="s">
         <v>428</v>
       </c>
@@ -10006,7 +9953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:15">
       <c r="C131" t="s">
         <v>484</v>
       </c>
@@ -10047,7 +9994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:15">
       <c r="C132" t="s">
         <v>285</v>
       </c>
@@ -10088,7 +10035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:15">
       <c r="C133" t="s">
         <v>81</v>
       </c>
@@ -10129,7 +10076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:15">
       <c r="C134" t="s">
         <v>81</v>
       </c>
@@ -10170,7 +10117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:15">
       <c r="C135" t="s">
         <v>174</v>
       </c>
@@ -10211,7 +10158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:15">
       <c r="C136" t="s">
         <v>612</v>
       </c>
@@ -10252,7 +10199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:15">
       <c r="C137" t="s">
         <v>639</v>
       </c>
@@ -10293,7 +10240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:15">
       <c r="C138" t="s">
         <v>91</v>
       </c>
@@ -10334,7 +10281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:15">
       <c r="C139" t="s">
         <v>551</v>
       </c>
@@ -10375,7 +10322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:15">
       <c r="C140" t="s">
         <v>404</v>
       </c>
@@ -10416,7 +10363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:15">
       <c r="C141" t="s">
         <v>345</v>
       </c>
@@ -10457,7 +10404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:15">
       <c r="C142" t="s">
         <v>327</v>
       </c>
@@ -10498,7 +10445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:15">
       <c r="C143" t="s">
         <v>327</v>
       </c>
@@ -10539,7 +10486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:15">
       <c r="C144" t="s">
         <v>109</v>
       </c>
@@ -10580,7 +10527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:15">
       <c r="C145" t="s">
         <v>371</v>
       </c>
@@ -10621,7 +10568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:15">
       <c r="C146" t="s">
         <v>357</v>
       </c>
@@ -10662,7 +10609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:15">
       <c r="C147" t="s">
         <v>466</v>
       </c>
@@ -10703,7 +10650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:15">
       <c r="C148" t="s">
         <v>466</v>
       </c>
@@ -10744,7 +10691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:15">
       <c r="C149" t="s">
         <v>66</v>
       </c>
@@ -10785,7 +10732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:15">
       <c r="C150" t="s">
         <v>401</v>
       </c>
@@ -10826,7 +10773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:15">
       <c r="C151" t="s">
         <v>715</v>
       </c>
@@ -10867,7 +10814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:15">
       <c r="C152" t="s">
         <v>621</v>
       </c>
@@ -10908,7 +10855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:15">
       <c r="C153" t="s">
         <v>563</v>
       </c>
@@ -10949,7 +10896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:15">
       <c r="C154" t="s">
         <v>563</v>
       </c>
@@ -10990,7 +10937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:15">
       <c r="C155" t="s">
         <v>386</v>
       </c>
@@ -11031,7 +10978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:15">
       <c r="C156" t="s">
         <v>581</v>
       </c>
@@ -11072,7 +11019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:15">
       <c r="C157" t="s">
         <v>168</v>
       </c>
@@ -11113,7 +11060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:15">
       <c r="C158" t="s">
         <v>168</v>
       </c>
@@ -11154,7 +11101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:15">
       <c r="C159" t="s">
         <v>422</v>
       </c>
@@ -11195,7 +11142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:15">
       <c r="C160" t="s">
         <v>697</v>
       </c>
@@ -11236,7 +11183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:15">
       <c r="C161" t="s">
         <v>660</v>
       </c>
@@ -11277,7 +11224,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:15">
       <c r="C162" t="s">
         <v>718</v>
       </c>
@@ -11318,7 +11265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:15">
       <c r="C163" t="s">
         <v>691</v>
       </c>
@@ -11359,7 +11306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:15">
       <c r="C164" t="s">
         <v>252</v>
       </c>
@@ -11400,7 +11347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:15">
       <c r="C165" t="s">
         <v>156</v>
       </c>
@@ -11441,7 +11388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:15">
       <c r="C166" t="s">
         <v>156</v>
       </c>
@@ -11482,7 +11429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:15">
       <c r="C167" t="s">
         <v>492</v>
       </c>
@@ -11523,7 +11470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:15">
       <c r="C168" t="s">
         <v>492</v>
       </c>
@@ -11564,7 +11511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:15">
       <c r="C169" t="s">
         <v>495</v>
       </c>
@@ -11605,7 +11552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:15">
       <c r="C170" t="s">
         <v>38</v>
       </c>
@@ -11646,7 +11593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:15">
       <c r="C171" t="s">
         <v>439</v>
       </c>
@@ -11687,7 +11634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:15">
       <c r="C172" t="s">
         <v>231</v>
       </c>
@@ -11728,7 +11675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:15">
       <c r="C173" t="s">
         <v>722</v>
       </c>
@@ -11769,7 +11716,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:15">
       <c r="C174" t="s">
         <v>207</v>
       </c>
@@ -11810,7 +11757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:15">
       <c r="C175" t="s">
         <v>207</v>
       </c>
@@ -11851,7 +11798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:15">
       <c r="C176" t="s">
         <v>377</v>
       </c>
@@ -11892,7 +11839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:15">
       <c r="C177" t="s">
         <v>554</v>
       </c>
@@ -11933,7 +11880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:15">
       <c r="C178" t="s">
         <v>180</v>
       </c>
@@ -11974,7 +11921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:15">
       <c r="C179" t="s">
         <v>180</v>
       </c>
@@ -12015,7 +11962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:15">
       <c r="C180" t="s">
         <v>195</v>
       </c>
@@ -12056,7 +12003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:15">
       <c r="C181" t="s">
         <v>219</v>
       </c>
@@ -12097,7 +12044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:15">
       <c r="C182" t="s">
         <v>569</v>
       </c>
@@ -12138,7 +12085,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:15">
       <c r="C183" t="s">
         <v>106</v>
       </c>
@@ -12179,7 +12126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:15">
       <c r="C184" t="s">
         <v>303</v>
       </c>
@@ -12220,7 +12167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:15">
       <c r="C185" t="s">
         <v>303</v>
       </c>
@@ -12261,7 +12208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:15">
       <c r="C186" t="s">
         <v>264</v>
       </c>
@@ -12302,7 +12249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:15">
       <c r="C187" t="s">
         <v>264</v>
       </c>
@@ -12343,7 +12290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:15">
       <c r="C188" t="s">
         <v>539</v>
       </c>
@@ -12384,7 +12331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:15">
       <c r="C189" t="s">
         <v>383</v>
       </c>
@@ -12425,7 +12372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:15">
       <c r="C190" t="s">
         <v>576</v>
       </c>
@@ -12466,7 +12413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:15">
       <c r="C191" t="s">
         <v>542</v>
       </c>
@@ -12507,7 +12454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:15">
       <c r="C192" t="s">
         <v>153</v>
       </c>
@@ -12548,7 +12495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:15">
       <c r="C193" t="s">
         <v>694</v>
       </c>
@@ -12589,7 +12536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:15">
       <c r="C194" t="s">
         <v>237</v>
       </c>
@@ -12630,7 +12577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:15">
       <c r="C195" t="s">
         <v>237</v>
       </c>
@@ -12671,7 +12618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:15">
       <c r="C196" t="s">
         <v>475</v>
       </c>
@@ -12712,7 +12659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:15">
       <c r="C197" t="s">
         <v>300</v>
       </c>
@@ -12753,7 +12700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:15">
       <c r="C198" t="s">
         <v>732</v>
       </c>
@@ -12794,7 +12741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:15">
       <c r="C199" t="s">
         <v>587</v>
       </c>
@@ -12835,7 +12782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:15">
       <c r="C200" t="s">
         <v>636</v>
       </c>
@@ -12876,7 +12823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:15">
       <c r="C201" t="s">
         <v>463</v>
       </c>
@@ -12917,7 +12864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:15">
       <c r="C202" t="s">
         <v>615</v>
       </c>
@@ -12958,7 +12905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:15">
       <c r="C203" t="s">
         <v>710</v>
       </c>
@@ -12999,7 +12946,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:15">
       <c r="C204" t="s">
         <v>62</v>
       </c>
@@ -13040,7 +12987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:15">
       <c r="C205" t="s">
         <v>478</v>
       </c>
@@ -13081,7 +13028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:15">
       <c r="C206" t="s">
         <v>478</v>
       </c>
@@ -13122,7 +13069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:15">
       <c r="C207" t="s">
         <v>545</v>
       </c>
@@ -13163,7 +13110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:15">
       <c r="C208" t="s">
         <v>663</v>
       </c>
@@ -13204,7 +13151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:15">
       <c r="C209" t="s">
         <v>177</v>
       </c>
@@ -13245,7 +13192,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:15">
       <c r="C210" t="s">
         <v>472</v>
       </c>
@@ -13286,7 +13233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:15">
       <c r="C211" t="s">
         <v>572</v>
       </c>
@@ -13327,7 +13274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:15">
       <c r="C212" t="s">
         <v>222</v>
       </c>
@@ -13368,7 +13315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:15">
       <c r="C213" t="s">
         <v>498</v>
       </c>
@@ -13409,7 +13356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:15">
       <c r="C214" t="s">
         <v>288</v>
       </c>
@@ -13450,7 +13397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:15">
       <c r="C215" t="s">
         <v>398</v>
       </c>
@@ -13491,7 +13438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:15">
       <c r="C216" t="s">
         <v>398</v>
       </c>
@@ -13532,7 +13479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:15">
       <c r="C217" t="s">
         <v>297</v>
       </c>
@@ -13573,7 +13520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:15">
       <c r="C218" t="s">
         <v>516</v>
       </c>
@@ -13614,7 +13561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:15">
       <c r="C219" t="s">
         <v>165</v>
       </c>
@@ -13655,7 +13602,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:15">
       <c r="C220" t="s">
         <v>599</v>
       </c>
@@ -13696,7 +13643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="221" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:15">
       <c r="C221" t="s">
         <v>33</v>
       </c>
@@ -13737,7 +13684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:15">
       <c r="C222" t="s">
         <v>330</v>
       </c>
@@ -13778,7 +13725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:15">
       <c r="C223" t="s">
         <v>330</v>
       </c>
@@ -13819,7 +13766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:15">
       <c r="C224" t="s">
         <v>677</v>
       </c>
@@ -13860,7 +13807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:15">
       <c r="C225" t="s">
         <v>249</v>
       </c>
@@ -13901,7 +13848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:15">
       <c r="C226" t="s">
         <v>228</v>
       </c>
@@ -13942,7 +13889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:15">
       <c r="C227" t="s">
         <v>144</v>
       </c>
@@ -13983,7 +13930,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:15">
       <c r="C228" t="s">
         <v>144</v>
       </c>
@@ -14024,7 +13971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:15">
       <c r="C229" t="s">
         <v>425</v>
       </c>
@@ -14065,7 +14012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:15">
       <c r="C230" t="s">
         <v>315</v>
       </c>
@@ -14106,7 +14053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:15">
       <c r="C231" t="s">
         <v>315</v>
       </c>
@@ -14147,7 +14094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:15">
       <c r="C232" t="s">
         <v>73</v>
       </c>
@@ -14188,7 +14135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:15">
       <c r="C233" t="s">
         <v>255</v>
       </c>
@@ -14229,7 +14176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:15">
       <c r="C234" t="s">
         <v>442</v>
       </c>
@@ -14270,7 +14217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:15">
       <c r="C235" t="s">
         <v>85</v>
       </c>
@@ -14311,7 +14258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:15">
       <c r="C236" t="s">
         <v>270</v>
       </c>
@@ -14352,7 +14299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:15">
       <c r="C237" t="s">
         <v>159</v>
       </c>
@@ -14393,7 +14340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:15">
       <c r="C238" t="s">
         <v>584</v>
       </c>
@@ -14434,7 +14381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:15">
       <c r="C239" t="s">
         <v>261</v>
       </c>
@@ -14475,7 +14422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:15">
       <c r="C240" t="s">
         <v>243</v>
       </c>
@@ -14516,7 +14463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:15">
       <c r="C241" t="s">
         <v>243</v>
       </c>
@@ -14557,7 +14504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:15">
       <c r="C242" t="s">
         <v>354</v>
       </c>
@@ -14598,7 +14545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:15">
       <c r="C243" t="s">
         <v>138</v>
       </c>
@@ -14639,7 +14586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:15">
       <c r="C244" t="s">
         <v>138</v>
       </c>
@@ -14680,7 +14627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:15">
       <c r="C245" t="s">
         <v>481</v>
       </c>
@@ -14721,7 +14668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:15">
       <c r="C246" t="s">
         <v>380</v>
       </c>
@@ -14762,7 +14709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:15">
       <c r="C247" t="s">
         <v>454</v>
       </c>
@@ -14803,7 +14750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:15">
       <c r="C248" t="s">
         <v>701</v>
       </c>
@@ -14844,7 +14791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:15">
       <c r="C249" t="s">
         <v>125</v>
       </c>
@@ -14885,7 +14832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:15">
       <c r="C250" t="s">
         <v>171</v>
       </c>
@@ -14926,7 +14873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:15">
       <c r="C251" t="s">
         <v>267</v>
       </c>
@@ -14967,7 +14914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:15">
       <c r="C252" t="s">
         <v>374</v>
       </c>
@@ -15008,7 +14955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:15">
       <c r="C253" t="s">
         <v>374</v>
       </c>
@@ -15049,7 +14996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:15">
       <c r="C254" t="s">
         <v>201</v>
       </c>
@@ -15090,7 +15037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:15">
       <c r="C255" t="s">
         <v>201</v>
       </c>
@@ -15131,7 +15078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:15">
       <c r="C256" t="s">
         <v>112</v>
       </c>
@@ -15172,7 +15119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:15">
       <c r="C257" t="s">
         <v>602</v>
       </c>
@@ -15213,7 +15160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:15">
       <c r="C258" t="s">
         <v>651</v>
       </c>
@@ -15254,7 +15201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:15">
       <c r="C259" t="s">
         <v>651</v>
       </c>
@@ -15295,7 +15242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:15">
       <c r="C260" t="s">
         <v>522</v>
       </c>
@@ -15336,7 +15283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:15">
       <c r="C261" t="s">
         <v>536</v>
       </c>
@@ -15377,7 +15324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:15">
       <c r="C262" t="s">
         <v>528</v>
       </c>
@@ -15418,7 +15365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:15">
       <c r="C263" t="s">
         <v>457</v>
       </c>
@@ -15459,7 +15406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:15">
       <c r="C264" t="s">
         <v>135</v>
       </c>
@@ -15500,7 +15447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="265" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:15">
       <c r="C265" t="s">
         <v>150</v>
       </c>
@@ -15541,7 +15488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:15">
       <c r="C266" t="s">
         <v>725</v>
       </c>
@@ -15582,7 +15529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:15">
       <c r="C267" t="s">
         <v>306</v>
       </c>
@@ -15625,9 +15572,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15635,7 +15581,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA94ACF5-A7FE-4215-AFA5-847EEB8418F0}">
   <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" customWidth="1"/>
@@ -15643,7 +15589,7 @@
     <col min="5" max="5" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5">
       <c r="B2" s="26" t="s">
         <v>4</v>
       </c>
@@ -15657,7 +15603,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>36</v>
       </c>
@@ -15674,7 +15620,7 @@
         <v>83883.965000000011</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>25</v>
       </c>
@@ -15688,7 +15634,7 @@
         <v>79705.644583333342</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -15702,7 +15648,7 @@
         <v>81976.441923076913</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>54</v>
       </c>
@@ -15716,7 +15662,7 @@
         <v>64441.299999999996</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>131</v>
       </c>
@@ -15730,7 +15676,7 @@
         <v>67242.51761904762</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>101</v>
       </c>
@@ -15744,7 +15690,7 @@
         <v>69806.945769230777</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>97</v>
       </c>
@@ -15758,7 +15704,7 @@
         <v>73109.377727272746</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5">
       <c r="B10" t="s">
         <v>58</v>
       </c>
@@ -15772,7 +15718,7 @@
         <v>66910.765555555554</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
         <v>32</v>
       </c>
@@ -15786,7 +15732,7 @@
         <v>74673.974761904756</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
         <v>124</v>
       </c>
@@ -15800,7 +15746,7 @@
         <v>75179.064482758593</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>50</v>
       </c>
@@ -15814,7 +15760,7 @@
         <v>66432.455882352937</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5">
       <c r="B14" t="s">
         <v>105</v>
       </c>
@@ -15836,18 +15782,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D14934F-A952-4240-80AA-42257F8DCDAB}">
   <dimension ref="B1:N98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14">
       <c r="B1" s="25" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14">
       <c r="B2" s="29" t="str" cm="1">
         <f t="array" ref="B2:N2">staff[#Headers]</f>
         <v>Emp ID</v>
@@ -15889,7 +15835,7 @@
         <v>Work Type</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14">
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3:N49">_xlfn._xlws.FILTER(staff[],staff[Salary]&gt;100000)</f>
         <v>PR00147</v>
@@ -15931,7 +15877,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14">
       <c r="B4" t="str">
         <v>PR00746</v>
       </c>
@@ -15972,7 +15918,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14">
       <c r="B5" t="str">
         <v>PR01159</v>
       </c>
@@ -16013,7 +15959,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14">
       <c r="B6" t="str">
         <v>PR02010</v>
       </c>
@@ -16054,7 +16000,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14">
       <c r="B7" t="str">
         <v>PR02208</v>
       </c>
@@ -16095,7 +16041,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14">
       <c r="B8" t="str">
         <v>PR02288</v>
       </c>
@@ -16136,7 +16082,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14">
       <c r="B9" t="str">
         <v>PR03886</v>
       </c>
@@ -16177,7 +16123,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14">
       <c r="B10" t="str">
         <v>PR04601</v>
       </c>
@@ -16218,7 +16164,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14">
       <c r="B11" t="str">
         <v>SQ00022</v>
       </c>
@@ -16259,7 +16205,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14">
       <c r="B12" t="str">
         <v>SQ00144</v>
       </c>
@@ -16300,7 +16246,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14">
       <c r="B13" t="str">
         <v>SQ00498</v>
       </c>
@@ -16341,7 +16287,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14">
       <c r="B14" t="str">
         <v>SQ01620</v>
       </c>
@@ -16382,7 +16328,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14">
       <c r="B15" t="str">
         <v>SQ02035</v>
       </c>
@@ -16423,7 +16369,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14">
       <c r="B16" t="str">
         <v>SQ02035</v>
       </c>
@@ -16464,7 +16410,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14">
       <c r="B17" t="str">
         <v>SQ02174</v>
       </c>
@@ -16505,7 +16451,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14">
       <c r="B18" t="str">
         <v>SQ02624</v>
       </c>
@@ -16546,7 +16492,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14">
       <c r="B19" t="str">
         <v>SQ02703</v>
       </c>
@@ -16587,7 +16533,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14">
       <c r="B20" t="str">
         <v>SQ03116</v>
       </c>
@@ -16628,7 +16574,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14">
       <c r="B21" t="str">
         <v>SQ03387</v>
       </c>
@@ -16669,7 +16615,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14">
       <c r="B22" t="str">
         <v>SQ03476</v>
       </c>
@@ -16710,7 +16656,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14">
       <c r="B23" t="str">
         <v>SQ03491</v>
       </c>
@@ -16751,7 +16697,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14">
       <c r="B24" t="str">
         <v>SQ03733</v>
       </c>
@@ -16792,7 +16738,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14">
       <c r="B25" t="str">
         <v>SQ04603</v>
       </c>
@@ -16833,7 +16779,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14">
       <c r="B26" t="str">
         <v>SQ04612</v>
       </c>
@@ -16874,7 +16820,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14">
       <c r="B27" t="str">
         <v>SQ04665</v>
       </c>
@@ -16915,7 +16861,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14">
       <c r="B28" t="str">
         <v>TN00579</v>
       </c>
@@ -16956,7 +16902,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14">
       <c r="B29" t="str">
         <v>TN01281</v>
       </c>
@@ -16997,7 +16943,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14">
       <c r="B30" t="str">
         <v>TN04058</v>
       </c>
@@ -17038,7 +16984,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14">
       <c r="B31" t="str">
         <v>TN04058</v>
       </c>
@@ -17079,7 +17025,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14">
       <c r="B32" t="str">
         <v>TN04246</v>
       </c>
@@ -17120,7 +17066,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14">
       <c r="B33" t="str">
         <v>TN04740</v>
       </c>
@@ -17161,7 +17107,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14">
       <c r="B34" t="str">
         <v>VT01684</v>
       </c>
@@ -17202,7 +17148,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14">
       <c r="B35" t="str">
         <v>VT01762</v>
       </c>
@@ -17243,7 +17189,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14">
       <c r="B36" t="str">
         <v>VT01893</v>
       </c>
@@ -17284,7 +17230,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14">
       <c r="B37" t="str">
         <v>VT01893</v>
       </c>
@@ -17325,7 +17271,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14">
       <c r="B38" t="str">
         <v>VT02491</v>
       </c>
@@ -17366,7 +17312,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14">
       <c r="B39" t="str">
         <v>VT02801</v>
       </c>
@@ -17407,7 +17353,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14">
       <c r="B40" t="str">
         <v>VT03421</v>
       </c>
@@ -17448,7 +17394,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14">
       <c r="B41" t="str">
         <v>VT03421</v>
       </c>
@@ -17489,7 +17435,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14">
       <c r="B42" t="str">
         <v>VT04028</v>
       </c>
@@ -17530,7 +17476,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14">
       <c r="B43" t="str">
         <v>VT04028</v>
       </c>
@@ -17571,7 +17517,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14">
       <c r="B44" t="str">
         <v>VT04093</v>
       </c>
@@ -17612,7 +17558,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14">
       <c r="B45" t="str">
         <v>VT04093</v>
       </c>
@@ -17653,7 +17599,7 @@
         <v>Part time</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14">
       <c r="B46" t="str">
         <v>VT04350</v>
       </c>
@@ -17694,7 +17640,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14">
       <c r="B47" t="str">
         <v>VT04350</v>
       </c>
@@ -17735,7 +17681,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14">
       <c r="B48" t="str">
         <v>VT04552</v>
       </c>
@@ -17776,7 +17722,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14">
       <c r="B49" t="str">
         <v>VT04681</v>
       </c>
@@ -17817,60 +17763,60 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14">
       <c r="I50" s="28"/>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14">
       <c r="I51" s="28"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14">
       <c r="I52" s="28"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14">
       <c r="I53" s="28"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14">
       <c r="I54" s="28"/>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14">
       <c r="I55" s="28"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14">
       <c r="I56" s="28"/>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14">
       <c r="I57" s="28"/>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14">
       <c r="I58" s="28"/>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14">
       <c r="I59" s="28"/>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14">
       <c r="I60" s="28"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14">
       <c r="I61" s="28"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14">
       <c r="I62" s="28"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14">
       <c r="I63" s="28"/>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14">
       <c r="I64" s="28"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14">
       <c r="I65" s="28"/>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14">
       <c r="I66" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14">
       <c r="B67" s="25" t="s">
         <v>766</v>
       </c>
@@ -17881,7 +17827,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14">
       <c r="B68" t="s">
         <v>767</v>
       </c>
@@ -17889,7 +17835,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14">
       <c r="B70" s="29" t="str" cm="1">
         <f t="array" ref="B70:F70">_xlfn.CHOOSECOLS(staff[#Headers], 1,2,3,5,6)</f>
         <v>Emp ID</v>
@@ -17907,7 +17853,7 @@
         <v>Salary</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14">
       <c r="B71" t="str" cm="1">
         <f t="array" ref="B71:F98">_xlfn.CHOOSECOLS(_xlfn._xlws.FILTER(staff[], staff[Salary]&gt;F67),1,2,3,5,6)</f>
         <v>PR00147</v>
@@ -17944,7 +17890,7 @@
         <v>114177.23</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14">
       <c r="B72" t="str">
         <v>PR00746</v>
       </c>
@@ -17979,7 +17925,7 @@
         <v>111049.84</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:14">
       <c r="B73" t="str">
         <v>PR01159</v>
       </c>
@@ -18014,7 +17960,7 @@
         <v>118442.54</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:14">
       <c r="B74" t="str">
         <v>PR02010</v>
       </c>
@@ -18049,7 +17995,7 @@
         <v>114772.32</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:14">
       <c r="B75" t="str">
         <v>PR03886</v>
       </c>
@@ -18084,7 +18030,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:14">
       <c r="B76" t="str">
         <v>SQ00022</v>
       </c>
@@ -18119,7 +18065,7 @@
         <v>109163.39</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:14">
       <c r="B77" t="str">
         <v>SQ00144</v>
       </c>
@@ -18154,7 +18100,7 @@
         <v>114425.19</v>
       </c>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:14">
       <c r="B78" t="str">
         <v>SQ00498</v>
       </c>
@@ -18189,7 +18135,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:14">
       <c r="B79" t="str">
         <v>SQ01620</v>
       </c>
@@ -18224,7 +18170,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:14">
       <c r="B80" t="str">
         <v>SQ02174</v>
       </c>
@@ -18259,7 +18205,7 @@
         <v>110906.35</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6">
       <c r="B81" t="str">
         <v>SQ02624</v>
       </c>
@@ -18276,7 +18222,7 @@
         <v>114772.32</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6">
       <c r="B82" t="str">
         <v>SQ03116</v>
       </c>
@@ -18293,7 +18239,7 @@
         <v>108872.77</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6">
       <c r="B83" t="str">
         <v>SQ03733</v>
       </c>
@@ -18310,7 +18256,7 @@
         <v>109143.17</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6">
       <c r="B84" t="str">
         <v>SQ04603</v>
       </c>
@@ -18327,7 +18273,7 @@
         <v>111229.47</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6">
       <c r="B85" t="str">
         <v>SQ04612</v>
       </c>
@@ -18344,7 +18290,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6">
       <c r="B86" t="str">
         <v>TN00579</v>
       </c>
@@ -18361,7 +18307,7 @@
         <v>109163.39</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6">
       <c r="B87" t="str">
         <v>TN01281</v>
       </c>
@@ -18378,7 +18324,7 @@
         <v>114425.19</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6">
       <c r="B88" t="str">
         <v>VT01893</v>
       </c>
@@ -18395,7 +18341,7 @@
         <v>112778.28</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6">
       <c r="B89" t="str">
         <v>VT01893</v>
       </c>
@@ -18412,7 +18358,7 @@
         <v>112778.28</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6">
       <c r="B90" t="str">
         <v>VT02491</v>
       </c>
@@ -18429,7 +18375,7 @@
         <v>114465.93</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6">
       <c r="B91" t="str">
         <v>VT02801</v>
       </c>
@@ -18446,7 +18392,7 @@
         <v>114691.03</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6">
       <c r="B92" t="str">
         <v>VT03421</v>
       </c>
@@ -18463,7 +18409,7 @@
         <v>113747.56</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6">
       <c r="B93" t="str">
         <v>VT03421</v>
       </c>
@@ -18480,7 +18426,7 @@
         <v>113747.56</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6">
       <c r="B94" t="str">
         <v>VT04028</v>
       </c>
@@ -18497,7 +18443,7 @@
         <v>111815.49</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6">
       <c r="B95" t="str">
         <v>VT04028</v>
       </c>
@@ -18514,7 +18460,7 @@
         <v>111815.49</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6">
       <c r="B96" t="str">
         <v>VT04093</v>
       </c>
@@ -18531,7 +18477,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6">
       <c r="B97" t="str">
         <v>VT04093</v>
       </c>
@@ -18548,7 +18494,7 @@
         <v>116767.63</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6">
       <c r="B98" t="str">
         <v>VT04681</v>
       </c>
@@ -18573,7 +18519,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5154C9-D555-4694-ADD9-3D6CAF5C334E}">
   <dimension ref="B1:I34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -18581,12 +18527,12 @@
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9">
       <c r="B1" s="25" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9">
       <c r="C3" s="33" t="s">
         <v>774</v>
       </c>
@@ -18597,7 +18543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9">
       <c r="B4" s="32" t="s">
         <v>771</v>
       </c>
@@ -18614,7 +18560,7 @@
         <v>28305.08</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9">
       <c r="B5" s="32" t="s">
         <v>772</v>
       </c>
@@ -18631,7 +18577,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" s="32" t="s">
         <v>773</v>
       </c>
@@ -18651,7 +18597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="C7" s="36">
         <f>LARGE(staff[Salary],G7)</f>
         <v>120000</v>
@@ -18668,7 +18614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9">
       <c r="C8" s="36">
         <f>LARGE(staff[Salary],G8)</f>
         <v>119022.49</v>
@@ -18685,7 +18631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9">
       <c r="C9" s="36">
         <f>LARGE(staff[Salary],G9)</f>
         <v>118976.16</v>
@@ -18702,7 +18648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9">
       <c r="C10" s="36">
         <f>LARGE(staff[Salary],G10)</f>
         <v>118442.54</v>
@@ -18719,7 +18665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9">
       <c r="B12" s="32" t="s">
         <v>773</v>
       </c>
@@ -18733,7 +18679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9">
       <c r="B13" s="35" t="s">
         <v>775</v>
       </c>
@@ -18743,85 +18689,85 @@
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9">
       <c r="C14" s="38">
         <v>119022.49</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="37"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9">
       <c r="C15" s="38">
         <v>118976.16</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="37"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9">
       <c r="C16" s="38">
         <v>118442.54</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="39">
         <v>116767.63</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3">
       <c r="C18" s="39">
         <v>116767.63</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:3">
       <c r="C19" s="39">
         <v>115191.38</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3">
       <c r="C20" s="39"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:3">
       <c r="C21" s="39"/>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:3">
       <c r="C22" s="39"/>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:3">
       <c r="C23" s="39"/>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:3">
       <c r="C24" s="39"/>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:3">
       <c r="C25" s="39"/>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:3">
       <c r="C26" s="39"/>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:3">
       <c r="C27" s="39"/>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:3">
       <c r="C28" s="39"/>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:3">
       <c r="C29" s="39"/>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:3">
       <c r="C30" s="39"/>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:3">
       <c r="C31" s="39"/>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:3">
       <c r="C32" s="39"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3">
       <c r="C33" s="39"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:3">
       <c r="C34" s="39"/>
     </row>
   </sheetData>
@@ -18832,18 +18778,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D90A22C-5C43-4295-8A8C-7B09D9961386}">
   <dimension ref="B1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6">
       <c r="B1" s="25" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6">
       <c r="B3" s="25" t="s">
         <v>777</v>
       </c>
@@ -18855,68 +18801,68 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6">
       <c r="B4" t="str" cm="1">
         <f t="array" ref="B4:B16">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
         <v>Accounting</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6">
       <c r="B5" t="str">
         <v>Business Development</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" t="str">
         <v>Business Growth</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6">
       <c r="B7" t="str">
         <v>Engineering</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" t="str">
         <v>Human Resources</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" t="str">
         <v>Legal</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6">
       <c r="B10" t="str">
         <v>Marketing</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6">
       <c r="B11" t="str">
         <v>Product Management</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6">
       <c r="B12" t="str">
         <v>Research and Development</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6">
       <c r="B13" t="str">
         <v>Sales</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6">
       <c r="B14" t="str">
         <v>Services</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6">
       <c r="B15" t="str">
         <v>Support</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6">
       <c r="B16" t="str">
         <v>Training</v>
       </c>
@@ -18929,7 +18875,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C16C26-306B-4A6B-A7E5-BFAE2DDA5D56}">
   <dimension ref="A1:T34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -18938,12 +18884,12 @@
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="B1" s="25" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="B4" t="s">
         <v>782</v>
       </c>
@@ -18954,7 +18900,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="44">
         <v>2</v>
       </c>
@@ -18970,7 +18916,7 @@
         <v>Edd</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="44">
         <v>3</v>
       </c>
@@ -18986,7 +18932,7 @@
         <v>MacKnockiter</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="44">
         <v>5</v>
       </c>
@@ -19002,7 +18948,7 @@
         <v>Accounting</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="44">
         <v>6</v>
       </c>
@@ -19018,7 +18964,7 @@
         <v>119022.49</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20">
       <c r="B17" t="s">
         <v>784</v>
       </c>
@@ -19026,18 +18972,18 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20">
       <c r="C18">
         <f>MATCH(C17,staff[Last Name],0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20">
       <c r="H19" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20">
       <c r="B20" t="s">
         <v>782</v>
       </c>
@@ -19090,7 +19036,7 @@
         <v>Full time</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20">
       <c r="B21" t="s">
         <v>777</v>
       </c>
@@ -19103,7 +19049,7 @@
         <v>Business Growth</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20">
       <c r="B22" t="s">
         <v>785</v>
       </c>
@@ -19120,62 +19066,62 @@
         <v>PR00113</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20">
       <c r="H23" t="str">
         <v>Van</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20">
       <c r="H24" t="str">
         <v>Tuxwell</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20">
       <c r="H25" t="str">
         <v>Female</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20">
       <c r="H26" t="str">
         <v>Business Growth</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20">
       <c r="H27">
         <v>80695.740000000005</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20">
       <c r="H28" t="str">
         <v>50k to 100k</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20">
       <c r="H29">
         <v>43360</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20">
       <c r="H30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20">
       <c r="H31" t="str">
         <v>Permanent</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20">
       <c r="H32" t="str">
         <v>Columbus, USA</v>
       </c>
     </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:8">
       <c r="H33">
         <v>5.7643835616438359</v>
       </c>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:8">
       <c r="H34" t="str">
         <v>Full time</v>
       </c>
@@ -19188,19 +19134,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB06BE3-4F27-4CF7-9219-06DC32D878E6}">
   <dimension ref="B1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7">
       <c r="B1" s="25" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7">
       <c r="B4" t="s">
         <v>789</v>
       </c>
@@ -19209,7 +19155,7 @@
         <v>Minerva Ricardot</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7">
       <c r="B8" t="s">
         <v>790</v>
       </c>
@@ -19230,7 +19176,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84496F37-ECDB-4C26-B430-CB3C0992D21F}">
   <dimension ref="B1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
@@ -19238,12 +19184,12 @@
     <col min="9" max="9" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9">
       <c r="B1" s="25" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9">
       <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
@@ -19254,7 +19200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9">
       <c r="B4" t="str" cm="1">
         <f t="array" ref="B4:D25">_xlfn._xlws.FILTER(staff[[Emp ID]:[Last Name]], MONTH(staff[Start Date])=3)</f>
         <v>PR00746</v>
@@ -19267,7 +19213,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9">
       <c r="B5" t="str">
         <v>PR00893</v>
       </c>
@@ -19279,7 +19225,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" t="str">
         <v>SQ00022</v>
       </c>
@@ -19291,7 +19237,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="B7" t="str">
         <v>SQ00105</v>
       </c>
@@ -19303,7 +19249,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9">
       <c r="B8" t="str">
         <v>SQ01519</v>
       </c>
@@ -19315,7 +19261,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9">
       <c r="B9" t="str">
         <v>SQ03112</v>
       </c>
@@ -19327,7 +19273,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9">
       <c r="B10" t="str">
         <v>SQ03625</v>
       </c>
@@ -19339,7 +19285,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9">
       <c r="B11" t="str">
         <v>SQ04612</v>
       </c>
@@ -19351,7 +19297,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9">
       <c r="B12" t="str">
         <v>TN01256</v>
       </c>
@@ -19363,7 +19309,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9">
       <c r="B13" t="str">
         <v>TN01256</v>
       </c>
@@ -19375,7 +19321,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9">
       <c r="B14" t="str">
         <v>TN01601</v>
       </c>
@@ -19387,7 +19333,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9">
       <c r="B15" t="str">
         <v>TN01601</v>
       </c>
@@ -19399,7 +19345,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9">
       <c r="B16" t="str">
         <v>TN04892</v>
       </c>
@@ -19411,7 +19357,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" t="str">
         <v>VT01762</v>
       </c>
@@ -19423,7 +19369,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" t="str">
         <v>VT01803</v>
       </c>
@@ -19435,7 +19381,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9">
       <c r="B19" t="str">
         <v>VT02417</v>
       </c>
@@ -19447,7 +19393,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9">
       <c r="B20" t="str">
         <v>VT03421</v>
       </c>
@@ -19459,7 +19405,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9">
       <c r="B21" t="str">
         <v>VT03421</v>
       </c>
@@ -19471,7 +19417,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9">
       <c r="B22" t="str">
         <v>VT03993</v>
       </c>
@@ -19483,7 +19429,7 @@
       </c>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9">
       <c r="B23" t="str">
         <v>VT04028</v>
       </c>
@@ -19495,7 +19441,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9">
       <c r="B24" t="str">
         <v>VT04028</v>
       </c>
@@ -19507,7 +19453,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9">
       <c r="B25" t="str">
         <v>VT04415</v>
       </c>
@@ -19527,7 +19473,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D88269-85D9-4BFB-B0AE-A65EC3D3FA73}">
   <dimension ref="B1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -19537,12 +19483,12 @@
     <col min="7" max="7" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9">
       <c r="B1" s="25" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9">
       <c r="B3" s="29" t="s">
         <v>795</v>
       </c>
@@ -19563,11 +19509,11 @@
       <c r="H3" s="30"/>
       <c r="I3" s="30"/>
     </row>
-    <row r="4" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="8.25" customHeight="1">
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
     </row>
-    <row r="5" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="30">
       <c r="B5" s="54" t="s">
         <v>4</v>
       </c>
@@ -19591,7 +19537,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" s="51" t="str" cm="1">
         <f t="array" ref="B6:B18">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
         <v>Accounting</v>
@@ -19619,7 +19565,7 @@
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="B7" s="52" t="str">
         <v>Business Development</v>
       </c>
@@ -19641,7 +19587,7 @@
       <c r="H7" s="52"/>
       <c r="I7" s="52"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9">
       <c r="B8" s="52" t="str">
         <v>Business Growth</v>
       </c>
@@ -19663,7 +19609,7 @@
       <c r="H8" s="52"/>
       <c r="I8" s="52"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9">
       <c r="B9" s="52" t="str">
         <v>Engineering</v>
       </c>
@@ -19685,7 +19631,7 @@
       <c r="H9" s="52"/>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9">
       <c r="B10" s="52" t="str">
         <v>Human Resources</v>
       </c>
@@ -19707,7 +19653,7 @@
       <c r="H10" s="52"/>
       <c r="I10" s="52"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9">
       <c r="B11" s="52" t="str">
         <v>Legal</v>
       </c>
@@ -19729,7 +19675,7 @@
       <c r="H11" s="52"/>
       <c r="I11" s="52"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9">
       <c r="B12" s="52" t="str">
         <v>Marketing</v>
       </c>
@@ -19751,7 +19697,7 @@
       <c r="H12" s="52"/>
       <c r="I12" s="52"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9">
       <c r="B13" s="52" t="str">
         <v>Product Management</v>
       </c>
@@ -19773,7 +19719,7 @@
       <c r="H13" s="52"/>
       <c r="I13" s="52"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9">
       <c r="B14" s="52" t="str">
         <v>Research and Development</v>
       </c>
@@ -19795,7 +19741,7 @@
       <c r="H14" s="52"/>
       <c r="I14" s="52"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9">
       <c r="B15" s="52" t="str">
         <v>Sales</v>
       </c>
@@ -19817,7 +19763,7 @@
       <c r="H15" s="52"/>
       <c r="I15" s="52"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9">
       <c r="B16" s="52" t="str">
         <v>Services</v>
       </c>
@@ -19839,7 +19785,7 @@
       <c r="H16" s="52"/>
       <c r="I16" s="52"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" s="52" t="str">
         <v>Support</v>
       </c>
@@ -19861,7 +19807,7 @@
       <c r="H17" s="52"/>
       <c r="I17" s="52"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" s="52" t="str">
         <v>Training</v>
       </c>
